--- a/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
+++ b/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\BookShelf-App\BookShelf-App\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EFA4BD9-1A10-47B4-8407-69A79029CA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28F605A-998C-4875-ACD9-2128B6685E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8160" yWindow="468" windowWidth="14892" windowHeight="11592" xr2:uid="{6F9BA980-EC11-4EDD-8B86-94156A86210F}"/>
   </bookViews>
@@ -38,12 +38,109 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <si>
+    <t>Test Case:</t>
+  </si>
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t>Date Executed:</t>
+  </si>
+  <si>
+    <t>RESULT:</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>TC-07</t>
+  </si>
+  <si>
+    <t>TC-08</t>
+  </si>
+  <si>
+    <t>TC-09</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>Open Library API Remote Search</t>
+  </si>
+  <si>
+    <t>Fallback Cover Image Handling</t>
+  </si>
+  <si>
+    <t>Local SQLite CRUD Operations</t>
+  </si>
+  <si>
+    <t>Reading Status Persistence</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Validated live payload parsing.</t>
+  </si>
+  <si>
+    <t>Confirmed placeholder displays when cover_i is null.</t>
+  </si>
+  <si>
+    <t>Resolved index attribute issue; books save/delete cleanly.</t>
+  </si>
+  <si>
+    <t>Status picker updates SavedBooks table properly.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -57,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,17 +162,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -86,6 +241,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C9164DCA-A4AC-49BB-B18F-7F14B46C98AA}" name="Table1" displayName="Table1" ref="B6:F23" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="B6:F23" xr:uid="{C9164DCA-A4AC-49BB-B18F-7F14B46C98AA}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D15501BF-C621-4B86-82FA-53610D6B30A5}" name="Test Case:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{46C21601-CF87-4B42-962F-3CE93A3C0A34}" name="Description:" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{44494DBF-0A21-40C9-B170-20656C11BD9C}" name="Date Executed:" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{FCFC73FD-F051-417E-A30C-2AF9968FD150}" name="RESULT:" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{B475B3F9-BEFF-4148-B74C-0C65F27CA0AF}" name="Notes:" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +574,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763BCA6D-F5EB-402F-AE4F-6747A12BB8EB}">
-  <dimension ref="A1"/>
+  <dimension ref="B5:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:6" s="2" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46261</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46261</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46261</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46261</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
+++ b/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\BookShelf-App\BookShelf-App\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28F605A-998C-4875-ACD9-2128B6685E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D459F1DE-DB80-40CF-8C18-140BA9035556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8160" yWindow="468" windowWidth="14892" windowHeight="11592" xr2:uid="{6F9BA980-EC11-4EDD-8B86-94156A86210F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Test Case:</t>
   </si>
@@ -111,15 +111,25 @@
   </si>
   <si>
     <t>Status picker updates SavedBooks table properly.</t>
+  </si>
+  <si>
+    <t>BookShelf Testing and Results</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -145,13 +155,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -181,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,10 +221,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -200,6 +241,98 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -210,24 +343,6 @@
         <sz val="14"/>
         <color theme="1"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -244,14 +359,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C9164DCA-A4AC-49BB-B18F-7F14B46C98AA}" name="Table1" displayName="Table1" ref="B6:F23" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C9164DCA-A4AC-49BB-B18F-7F14B46C98AA}" name="Table1" displayName="Table1" ref="B6:F23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="B6:F23" xr:uid="{C9164DCA-A4AC-49BB-B18F-7F14B46C98AA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D15501BF-C621-4B86-82FA-53610D6B30A5}" name="Test Case:" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{46C21601-CF87-4B42-962F-3CE93A3C0A34}" name="Description:" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{44494DBF-0A21-40C9-B170-20656C11BD9C}" name="Date Executed:" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{FCFC73FD-F051-417E-A30C-2AF9968FD150}" name="RESULT:" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{B475B3F9-BEFF-4148-B74C-0C65F27CA0AF}" name="Notes:" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D15501BF-C621-4B86-82FA-53610D6B30A5}" name="Test Case:" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{46C21601-CF87-4B42-962F-3CE93A3C0A34}" name="Description:" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{44494DBF-0A21-40C9-B170-20656C11BD9C}" name="Date Executed:" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{FCFC73FD-F051-417E-A30C-2AF9968FD150}" name="RESULT:" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{B475B3F9-BEFF-4148-B74C-0C65F27CA0AF}" name="Notes:" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -574,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763BCA6D-F5EB-402F-AE4F-6747A12BB8EB}">
-  <dimension ref="B5:F16"/>
+  <dimension ref="B3:F39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -586,124 +701,321 @@
     <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="2:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
     <row r="5" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:6" s="2" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:6" s="3" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="6">
         <v>46261</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="2:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="6">
         <v>46261</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="2:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="6">
         <v>46261</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="2:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="6">
         <v>46261</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="7"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="7"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B19" s="7"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B20" s="7"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="7"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="7"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="7"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="7"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <mergeCells count="1">
+    <mergeCell ref="B3:F3"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
+++ b/BookShelf-App/Docs/BookShelf_Test_Plan_And_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\BookShelf-App\BookShelf-App\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D459F1DE-DB80-40CF-8C18-140BA9035556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA3AA09-5128-4891-91FF-20B41D74A7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8160" yWindow="468" windowWidth="14892" windowHeight="11592" xr2:uid="{6F9BA980-EC11-4EDD-8B86-94156A86210F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Test Case:</t>
   </si>
@@ -114,6 +114,60 @@
   </si>
   <si>
     <t>BookShelf Testing and Results</t>
+  </si>
+  <si>
+    <t>Offline Connectivity Detection &amp; Banner</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>TC-13</t>
+  </si>
+  <si>
+    <t>TC-14</t>
+  </si>
+  <si>
+    <t>TC-15</t>
+  </si>
+  <si>
+    <t>TC-16</t>
+  </si>
+  <si>
+    <t>Personal Notes &amp; Star Ratings Persistence</t>
+  </si>
+  <si>
+    <t>Local Search &amp; Reading Status Filtering</t>
+  </si>
+  <si>
+    <t>Native Book Share Feature</t>
+  </si>
+  <si>
+    <t>Annual Reading Goal Challenge Widget</t>
+  </si>
+  <si>
+    <t>Collection Sorting &amp; Enlarged Covers</t>
+  </si>
+  <si>
+    <t>Verified dynamic LINQ sorting (Date Saved, Title A–Z, Rating) and enlarged high-res API cover image rendering (120x170px).</t>
+  </si>
+  <si>
+    <t>Verified progress bar and text counter update dynamically as books are marked 'Completed' (e.g. 1/10).</t>
+  </si>
+  <si>
+    <t>Verified 'Share Book' button launches native OS share sheet with title, author, and Open Library URL.</t>
+  </si>
+  <si>
+    <t>Verified live text search filtering title/author and status picker filtering on MyBooksPage.</t>
+  </si>
+  <si>
+    <t>Verified star ratings (0–5) and custom text notes save back to SQLite database (bookshelf_v4.db3).</t>
+  </si>
+  <si>
+    <t>Verified red warning banner appears and search input disables when disconnected from network.</t>
   </si>
 </sst>
 </file>
@@ -796,97 +850,157 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="78" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="7"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="7"/>
+      <c r="B18" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="7"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="7"/>
+      <c r="B19" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="7"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="7"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="7"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="7"/>
